--- a/Example Data/Acquisition_Times_Template.xlsx
+++ b/Example Data/Acquisition_Times_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/sebastian_stumpf_unibe_ch/Documents/PhD/ICP-Base/LAICPMS Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unibe365-my.sharepoint.com/personal/sebastian_stumpf_unibe_ch/Documents/PhD/ICP-Base/ICP-Base_dev/Example Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="223" documentId="11_AD4DB114E441178AC67DF4EAB656CEA0693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{375114DC-F902-4F2B-8F37-5181BE06E0BB}"/>
+  <xr:revisionPtr revIDLastSave="254" documentId="11_AD4DB114E441178AC67DF4EAB656CEA0693EDF1D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16476B85-2091-49F0-A17F-0D3DC99DEE05}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28860" yWindow="195" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
@@ -25,34 +25,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Acquisition_Times</t>
   </si>
   <si>
-    <t>16:02:00</t>
-  </si>
-  <si>
-    <t>16:06:00</t>
-  </si>
-  <si>
-    <t>16:03:00</t>
-  </si>
-  <si>
-    <t>16:04:00</t>
-  </si>
-  <si>
-    <t>16:05:00</t>
-  </si>
-  <si>
-    <t>16:08:00</t>
+    <t>2026-06-07 23:15:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:18:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:21:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:24:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:27:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:30:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:33:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:36:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:39:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:42:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:45:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:48:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:51:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:54:00</t>
+  </si>
+  <si>
+    <t>2026-06-07 23:57:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:00:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:03:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:06:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:09:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:12:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:15:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:18:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:21:00</t>
+  </si>
+  <si>
+    <t>2026-06-08 00:24:00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -65,6 +119,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -87,10 +146,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -372,68 +434,515 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBBF67B9-CA96-453C-8799-3892A58FC264}">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:C143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C2" s="2"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="2"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="2"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C6" s="2"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C7" s="2"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="C9" s="2"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="1"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="1"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="1"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="1"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="1"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="1"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="1"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="1"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="1"/>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1"/>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="1"/>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="1"/>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="1"/>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="1"/>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="1"/>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="1"/>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A122" s="1"/>
+    </row>
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A123" s="1"/>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A124" s="1"/>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A125" s="1"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A126" s="1"/>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A127" s="1"/>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A128" s="1"/>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A129" s="1"/>
+    </row>
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A130" s="1"/>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A131" s="1"/>
+    </row>
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A132" s="1"/>
+    </row>
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A133" s="1"/>
+    </row>
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A134" s="1"/>
+    </row>
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A135" s="1"/>
+    </row>
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A136" s="1"/>
+    </row>
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A137" s="1"/>
+    </row>
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A138" s="1"/>
+    </row>
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A139" s="1"/>
+    </row>
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A140" s="1"/>
+    </row>
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A141" s="1"/>
+    </row>
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A142" s="1"/>
+    </row>
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A143" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
